--- a/TestCASshort.xlsx
+++ b/TestCASshort.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arche/Documents/Python/ARCHEscreeningTool/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{121E4533-B208-A34E-92D9-963C0E0A6B39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2308110-F62B-0D4D-9FF6-EF48D816053E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28580" yWindow="1060" windowWidth="27720" windowHeight="17440" xr2:uid="{AC7C4B23-1DA4-2B48-871A-9902A8034EEE}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Name</t>
   </si>
@@ -54,6 +54,9 @@
   </si>
   <si>
     <t>141-62-8</t>
+  </si>
+  <si>
+    <t>119344-86-4</t>
   </si>
 </sst>
 </file>
@@ -489,7 +492,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{219314F5-F3E4-514C-9E76-324895DDE06E}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
@@ -520,6 +523,11 @@
         <v>5</v>
       </c>
     </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TestCASshort.xlsx
+++ b/TestCASshort.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arche/Documents/Python/ARCHEscreeningTool/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2308110-F62B-0D4D-9FF6-EF48D816053E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41734DE7-4A33-AD45-938B-260480F6A0B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28580" yWindow="1060" windowWidth="27720" windowHeight="17440" xr2:uid="{AC7C4B23-1DA4-2B48-871A-9902A8034EEE}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Name</t>
   </si>
@@ -57,6 +57,9 @@
   </si>
   <si>
     <t>119344-86-4</t>
+  </si>
+  <si>
+    <t>68213-23-0</t>
   </si>
 </sst>
 </file>
@@ -492,7 +495,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{219314F5-F3E4-514C-9E76-324895DDE06E}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
@@ -528,6 +531,11 @@
         <v>6</v>
       </c>
     </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
